--- a/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-301_CALIFICADO.xlsx
@@ -1133,15 +1133,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>111001098888</t>
+          <t>111001098868</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4898,15 +4902,19 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>111001098888</t>
+          <t>111001098868</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LUIS-EDUARDO-MORA-OSEJO-(IED)-301_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -962,7 +954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1133,11 +1125,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1145,7 +1133,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1336,11 +1324,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1348,7 +1332,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1539,11 +1523,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1551,7 +1531,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1742,11 +1722,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1754,7 +1730,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1945,11 +1921,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -1957,7 +1929,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2148,11 +2120,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2160,7 +2128,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2351,11 +2319,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2363,7 +2327,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2554,11 +2518,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2566,7 +2526,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2749,11 +2709,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2761,7 +2717,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2952,11 +2908,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -2964,7 +2916,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3139,11 +3091,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3151,7 +3099,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3338,11 +3286,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3350,7 +3294,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3537,11 +3481,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3549,7 +3489,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3740,11 +3680,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3752,7 +3688,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3939,11 +3875,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -3951,7 +3883,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4142,11 +4074,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4154,7 +4082,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4341,11 +4269,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4353,7 +4277,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4544,11 +4468,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4556,7 +4476,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4739,11 +4659,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4751,7 +4667,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4902,11 +4818,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -4914,7 +4826,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5105,11 +5017,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5117,7 +5025,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5304,11 +5212,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5316,7 +5220,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5507,11 +5411,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5519,7 +5419,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5710,11 +5610,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5722,7 +5618,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5909,11 +5805,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -5921,7 +5813,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6112,11 +6004,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6124,7 +6012,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6315,11 +6203,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6327,7 +6211,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6518,11 +6402,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6530,7 +6410,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6721,11 +6601,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6733,7 +6609,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -6868,11 +6744,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -6880,7 +6752,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7067,11 +6939,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7079,7 +6947,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7246,11 +7114,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7258,7 +7122,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7449,11 +7313,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7461,7 +7321,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7648,11 +7508,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7660,7 +7516,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7851,11 +7707,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -7863,7 +7715,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8054,11 +7906,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098868</t>
@@ -8066,7 +7914,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LUIS EDUARDO MORA OSEJO (IED)</t>
+          <t>COLEGIO LUIS EDUARDO MORA OSEJO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
